--- a/models/sovereigns/Morocco_Sovereign_Model.xlsx
+++ b/models/sovereigns/Morocco_Sovereign_Model.xlsx
@@ -702,16 +702,34 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>4.9</v>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -892,16 +910,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>-3.1</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -909,16 +945,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>1.82</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1060,16 +1114,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>194.333</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Morocco_Sovereign_Model.xlsx
+++ b/models/sovereigns/Morocco_Sovereign_Model.xlsx
@@ -685,16 +685,34 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>-0.3333</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IMF CPI database</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IMF CPI database, all items, y/y % change, monthly (auto-filled; a run's sourced point replaces it unless older)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -755,7 +773,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>66.5</v>
+        <v>67.2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -764,7 +782,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -779,7 +797,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Treasury debt</t>
+          <t>Central government (Treasury) debt</t>
         </is>
       </c>
     </row>
@@ -807,7 +825,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -816,7 +834,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -829,11 +847,7 @@
           <t>Sep-26</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>central government budget</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -868,7 +882,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Sep-26 (central government)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -881,11 +895,7 @@
           <t>Sep-26</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>approximate</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -990,7 +1000,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>end-2026E</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1005,7 +1015,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>projection: MAD 502.8bn official FX reserves</t>
+          <t>Bank Al-Maghrib official FX reserves, MAD 502.8bn projected end-2026 (gold inclusion not stated)</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1052,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>end-2026E</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib</t>
+          <t>Bank Al-Maghrib (prospective imports of goods and services)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1307,7 +1317,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FCL (2-year, precautionary)</t>
+          <t>Flexible Credit Line (2-year, precautionary)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1330,7 +1340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1344,25 +1354,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2027F</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -1378,7 +1393,8 @@
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1390,7 +1406,8 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1400,13 +1417,14 @@
       </c>
       <c r="B4" s="2" t="n"/>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Bank Al-Maghrib, Sep-26</t>
         </is>
@@ -1422,7 +1440,8 @@
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="n"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1430,15 +1449,20 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>-4.3</v>
+      </c>
       <c r="C6" s="2" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>-3.5</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="E6" s="2" t="n">
         <v>-3</v>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Ministry of Economy and Finance, Sep-26</t>
         </is>
@@ -1454,7 +1478,8 @@
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1463,18 +1488,21 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>67.7</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="D8" s="2" t="n">
         <v>67.2</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="E8" s="2" t="n">
         <v>66.5</v>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ministry of Economy and Finance, Sep-26</t>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ministry of Economy and Finance, Sep-26 (central government Treasury debt)</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1516,8 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1499,8 +1528,15 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="E10" s="2" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bank Al-Maghrib, Sep-26 (projection, MAD 502.8bn)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1512,7 +1548,8 @@
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1524,7 +1561,8 @@
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Morocco_Sovereign_Model.xlsx
+++ b/models/sovereigns/Morocco_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/morocco.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/morocco.json</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -792,12 +792,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government (Treasury) debt</t>
+          <t>central government (Treasury) debt</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sep-26 (central government)</t>
+          <t>central government, latest (period not specified in source)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>end-2026E</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib official FX reserves, MAD 502.8bn projected end-2026 (gold inclusion not stated)</t>
+          <t>official FX reserves (MAD 502.8bn), Bank Al-Maghrib projection</t>
         </is>
       </c>
     </row>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>end-2026E, prospective imports of goods and services</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib (prospective imports of goods and services)</t>
+          <t>Bank Al-Maghrib</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib, Sep-26</t>
+          <t>Bank Al-Maghrib, 30-Sep-26</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, Sep-26</t>
+          <t>Ministry of Economy and Finance, 30-Sep-26 (central government; 2026E is the Finance Law target)</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, Sep-26 (central government Treasury debt)</t>
+          <t>Ministry of Economy and Finance, 30-Sep-26 (central government Treasury debt)</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib, Sep-26 (projection, MAD 502.8bn)</t>
+          <t>Bank Al-Maghrib, 30-Sep-26 (official FX reserves, projection; MAD 502.8bn converted at ~$55.65bn as stated in source)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Morocco_Sovereign_Model.xlsx
+++ b/models/sovereigns/Morocco_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>central government (Treasury) debt</t>
+          <t>Central government treasury debt</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance</t>
+          <t>Ministry of Economy and Finance (central government budget deficit)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>central government, latest (period not specified in source)</t>
+          <t>latest (period not stated)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance</t>
+          <t>Ministry of Economy and Finance (interest expenditure / central government revenues)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>end-2026E</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official FX reserves (MAD 502.8bn), Bank Al-Maghrib projection</t>
+          <t>Bank Al-Maghrib official FX reserves, projected end-2026 (MAD 502.8bn)</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>end-2026E, prospective imports of goods and services</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib</t>
+          <t>Bank Al-Maghrib (prospective imports of goods and services)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Flexible Credit Line (2-year, precautionary)</t>
+          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review concluded Mar-26</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1464,7 +1464,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, 30-Sep-26 (central government; 2026E is the Finance Law target)</t>
+          <t>Ministry of Economy and Finance, 30-Sep-26 (2026E is the Finance Law target)</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, 30-Sep-26 (central government Treasury debt)</t>
+          <t>Ministry of Economy and Finance, 30-Sep-26 (central government treasury debt)</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib, 30-Sep-26 (official FX reserves, projection; MAD 502.8bn converted at ~$55.65bn as stated in source)</t>
+          <t>Bank Al-Maghrib, 30-Sep-26 (official FX reserves, MAD 502.8bn converted as stated)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Morocco_Sovereign_Model.xlsx
+++ b/models/sovereigns/Morocco_Sovereign_Model.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -792,12 +792,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government treasury debt</t>
+          <t>Central government (Treasury) debt</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance (central government budget deficit)</t>
+          <t>Ministry of Economy and Finance</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -882,17 +882,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>latest (period not stated)</t>
+          <t>latest (central government)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance (interest expenditure / central government revenues)</t>
+          <t>Ministry of Economy and Finance</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>end-2026F</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib official FX reserves, projected end-2026 (MAD 502.8bn)</t>
+          <t>Bank Al-Maghrib official foreign exchange reserves, projected (MAD 502.8bn)</t>
         </is>
       </c>
     </row>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>end-2026F (prospective imports of goods and services)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib (prospective imports of goods and services)</t>
+          <t>Bank Al-Maghrib</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review concluded Mar-26</t>
+          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review concluded Mar-26; also RSF (SDR 1.0bn, approved Sep-23)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib, 30-Sep-26</t>
+          <t>Bank Al-Maghrib, Sep-26</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, 30-Sep-26 (2026E is the Finance Law target)</t>
+          <t>Ministry of Economy and Finance, Sep-26 (2026E is the Finance Law budget target)</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, 30-Sep-26 (central government treasury debt)</t>
+          <t>Ministry of Economy and Finance, Sep-26 (central government Treasury debt)</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib, 30-Sep-26 (official FX reserves, MAD 502.8bn converted as stated)</t>
+          <t>Bank Al-Maghrib, Sep-26 (official FX reserves, end-2026 projection)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Morocco_Sovereign_Model.xlsx
+++ b/models/sovereigns/Morocco_Sovereign_Model.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -792,12 +792,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government (Treasury) debt</t>
+          <t>Central government treasury debt</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>latest (central government)</t>
+          <t>central government, latest (Sep-26 report)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>end-2026F</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib official foreign exchange reserves, projected (MAD 502.8bn)</t>
+          <t>Bank Al-Maghrib official FX reserves, projected end-2026 (MAD 502.8bn)</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>end-2026F (prospective imports of goods and services)</t>
+          <t>2026E (prospective imports of goods and services)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review concluded Mar-26; also RSF (SDR 1.0bn, approved Sep-23)</t>
+          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review completed Mar-26; RSF SDR 1.0bn approved Sep-23</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib, Sep-26</t>
+          <t>Bank Al-Maghrib, 30-Sep-26</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, Sep-26 (2026E is the Finance Law budget target)</t>
+          <t>Ministry of Economy and Finance (central government), 30-Sep-26</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, Sep-26 (central government Treasury debt)</t>
+          <t>Ministry of Economy and Finance (central government treasury debt), 30-Sep-26</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib, Sep-26 (official FX reserves, end-2026 projection)</t>
+          <t>Bank Al-Maghrib (projection, MAD 502.8bn converted ~USD 55.65bn), 30-Sep-26</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Morocco_Sovereign_Model.xlsx
+++ b/models/sovereigns/Morocco_Sovereign_Model.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Central government treasury debt</t>
+          <t>central government (Treasury) debt</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance</t>
+          <t>Ministry of Economy and Finance (central government budget balance)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>central government, latest (Sep-26 report)</t>
+          <t>latest (Sep-26 report)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance</t>
+          <t>Ministry of Economy and Finance (interest expenditure / central government revenues)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib official FX reserves, projected end-2026 (MAD 502.8bn)</t>
+          <t>official FX reserves, Bank Al-Maghrib projection for end-2026 (MAD 502.8bn)</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026E (prospective imports of goods and services)</t>
+          <t>2026E</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib</t>
+          <t>Bank Al-Maghrib (prospective imports of goods and services)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Flexible Credit Line (2-year, precautionary); Mid-Term Review completed Mar-26; RSF SDR 1.0bn approved Sep-23</t>
+          <t>Flexible Credit Line (2-year, precautionary)</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1464,7 +1464,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance (central government), 30-Sep-26</t>
+          <t>Ministry of Economy and Finance, 30-Sep-26 (2026E is the Finance Law target)</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance (central government treasury debt), 30-Sep-26</t>
+          <t>Ministry of Economy and Finance, 30-Sep-26 (central government debt; 2026E projected)</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib (projection, MAD 502.8bn converted ~USD 55.65bn), 30-Sep-26</t>
+          <t>Bank Al-Maghrib, 30-Sep-26 (end-2026 projection, MAD 502.8bn converted at ~$55.65bn)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Morocco_Sovereign_Model.xlsx
+++ b/models/sovereigns/Morocco_Sovereign_Model.xlsx
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -792,12 +792,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>central government (Treasury) debt</t>
+          <t>Central government treasury debt</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance (central government budget balance)</t>
+          <t>Ministry of Economy and Finance (central government budget deficit)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -882,17 +882,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>latest (Sep-26 report)</t>
+          <t>2025/26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance (interest expenditure / central government revenues)</t>
+          <t>Ministry of Economy and Finance (interest expenditure, central government revenues; approximate)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official FX reserves, Bank Al-Maghrib projection for end-2026 (MAD 502.8bn)</t>
+          <t>Bank Al-Maghrib official FX reserves, projection for end-2026 (MAD 502.8bn); gold treatment not stated</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib, 30-Sep-26</t>
+          <t>Bank Al-Maghrib, Sep-26</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, 30-Sep-26 (2026E is the Finance Law target)</t>
+          <t>Ministry of Economy and Finance, Sep-26 (2026E is the Finance Law budget target)</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ministry of Economy and Finance, 30-Sep-26 (central government debt; 2026E projected)</t>
+          <t>Ministry of Economy and Finance, Sep-26 (central government treasury debt)</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       <c r="F10" s="2" t="n"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bank Al-Maghrib, 30-Sep-26 (end-2026 projection, MAD 502.8bn converted at ~$55.65bn)</t>
+          <t>Bank Al-Maghrib, Sep-26 (projection; MAD 502.8bn converted at ~$55.65bn per report)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Morocco_Sovereign_Model.xlsx
+++ b/models/sovereigns/Morocco_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/morocco.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/morocco.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Morocco_Sovereign_Model.xlsx
+++ b/models/sovereigns/Morocco_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/morocco.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/morocco.json</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/models/sovereigns/Morocco_Sovereign_Model.xlsx
+++ b/models/sovereigns/Morocco_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/morocco.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/morocco.json</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-0.3333</v>
+        <v>0.4992</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
